--- a/artfynd/A 51287-2025 artfynd.xlsx
+++ b/artfynd/A 51287-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111947464</v>
+        <v>111947450</v>
       </c>
       <c r="B2" t="n">
-        <v>89706</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533802</v>
+        <v>533826</v>
       </c>
       <c r="R2" t="n">
-        <v>7040172</v>
+        <v>7040080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111947475</v>
+        <v>111947435</v>
       </c>
       <c r="B3" t="n">
-        <v>78746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533807</v>
+        <v>533712</v>
       </c>
       <c r="R3" t="n">
-        <v>7040253</v>
+        <v>7040111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111947448</v>
+        <v>111947441</v>
       </c>
       <c r="B4" t="n">
-        <v>78647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533870</v>
+        <v>533758</v>
       </c>
       <c r="R4" t="n">
-        <v>7040086</v>
+        <v>7040062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111947449</v>
+        <v>111947468</v>
       </c>
       <c r="B5" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533834</v>
+        <v>533776</v>
       </c>
       <c r="R5" t="n">
-        <v>7040041</v>
+        <v>7040228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111947473</v>
+        <v>111947466</v>
       </c>
       <c r="B6" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533807</v>
+        <v>533788</v>
       </c>
       <c r="R6" t="n">
-        <v>7040253</v>
+        <v>7040203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111947459</v>
+        <v>111947452</v>
       </c>
       <c r="B7" t="n">
-        <v>77403</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533705</v>
+        <v>533857</v>
       </c>
       <c r="R7" t="n">
-        <v>7040162</v>
+        <v>7040125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1260,7 @@
         <v>111947467</v>
       </c>
       <c r="B8" t="n">
-        <v>79580</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111947480</v>
+        <v>111947451</v>
       </c>
       <c r="B9" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533976</v>
+        <v>533850</v>
       </c>
       <c r="R9" t="n">
-        <v>7040208</v>
+        <v>7040106</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111947451</v>
+        <v>111947453</v>
       </c>
       <c r="B10" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533851</v>
+        <v>533775</v>
       </c>
       <c r="R10" t="n">
-        <v>7040105</v>
+        <v>7040099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111947452</v>
+        <v>111947464</v>
       </c>
       <c r="B11" t="n">
-        <v>79580</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533857</v>
+        <v>533801</v>
       </c>
       <c r="R11" t="n">
-        <v>7040126</v>
+        <v>7040172</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111947460</v>
+        <v>111947433</v>
       </c>
       <c r="B12" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533705</v>
+        <v>533712</v>
       </c>
       <c r="R12" t="n">
-        <v>7040162</v>
+        <v>7040111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111947471</v>
+        <v>111947481</v>
       </c>
       <c r="B13" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533764</v>
+        <v>533976</v>
       </c>
       <c r="R13" t="n">
-        <v>7040257</v>
+        <v>7040208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111947447</v>
+        <v>111947449</v>
       </c>
       <c r="B14" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533878</v>
+        <v>533834</v>
       </c>
       <c r="R14" t="n">
-        <v>7040114</v>
+        <v>7040042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111947450</v>
+        <v>111947476</v>
       </c>
       <c r="B15" t="n">
-        <v>94301</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533826</v>
+        <v>533808</v>
       </c>
       <c r="R15" t="n">
-        <v>7040080</v>
+        <v>7040253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111947478</v>
+        <v>111947434</v>
       </c>
       <c r="B16" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533832</v>
+        <v>533712</v>
       </c>
       <c r="R16" t="n">
-        <v>7040203</v>
+        <v>7040111</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111947477</v>
+        <v>111947465</v>
       </c>
       <c r="B17" t="n">
-        <v>77738</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6450</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533816</v>
+        <v>533812</v>
       </c>
       <c r="R17" t="n">
-        <v>7040225</v>
+        <v>7040197</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111947470</v>
+        <v>111947446</v>
       </c>
       <c r="B18" t="n">
-        <v>78242</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533763</v>
+        <v>533902</v>
       </c>
       <c r="R18" t="n">
-        <v>7040240</v>
+        <v>7040125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111947465</v>
+        <v>111947479</v>
       </c>
       <c r="B19" t="n">
-        <v>89478</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533812</v>
+        <v>533909</v>
       </c>
       <c r="R19" t="n">
-        <v>7040197</v>
+        <v>7040241</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111947466</v>
+        <v>111947432</v>
       </c>
       <c r="B20" t="n">
-        <v>90113</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533788</v>
+        <v>533687</v>
       </c>
       <c r="R20" t="n">
-        <v>7040203</v>
+        <v>7040125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111947468</v>
+        <v>111947463</v>
       </c>
       <c r="B21" t="n">
-        <v>77321</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533776</v>
+        <v>533717</v>
       </c>
       <c r="R21" t="n">
-        <v>7040228</v>
+        <v>7040212</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111947442</v>
+        <v>111947440</v>
       </c>
       <c r="B22" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533853</v>
+        <v>533758</v>
       </c>
       <c r="R22" t="n">
-        <v>7040038</v>
+        <v>7040062</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111947446</v>
+        <v>111947457</v>
       </c>
       <c r="B23" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533902</v>
+        <v>533703</v>
       </c>
       <c r="R23" t="n">
-        <v>7040125</v>
+        <v>7040176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111947463</v>
+        <v>111947473</v>
       </c>
       <c r="B24" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533717</v>
+        <v>533808</v>
       </c>
       <c r="R24" t="n">
-        <v>7040212</v>
+        <v>7040253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111947476</v>
+        <v>111947480</v>
       </c>
       <c r="B25" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533807</v>
+        <v>533976</v>
       </c>
       <c r="R25" t="n">
-        <v>7040253</v>
+        <v>7040208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111947479</v>
+        <v>111947437</v>
       </c>
       <c r="B26" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533909</v>
+        <v>533726</v>
       </c>
       <c r="R26" t="n">
-        <v>7040241</v>
+        <v>7040056</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111947445</v>
+        <v>111947460</v>
       </c>
       <c r="B27" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533895</v>
+        <v>533705</v>
       </c>
       <c r="R27" t="n">
-        <v>7040097</v>
+        <v>7040162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111947461</v>
+        <v>111947477</v>
       </c>
       <c r="B28" t="n">
-        <v>78242</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533705</v>
+        <v>533816</v>
       </c>
       <c r="R28" t="n">
-        <v>7040162</v>
+        <v>7040225</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111947481</v>
+        <v>111947439</v>
       </c>
       <c r="B29" t="n">
-        <v>91002</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3445,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533976</v>
+        <v>533737</v>
       </c>
       <c r="R29" t="n">
-        <v>7040208</v>
+        <v>7040063</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,12 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111947456</v>
+        <v>111947461</v>
       </c>
       <c r="B30" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533757</v>
+        <v>533705</v>
       </c>
       <c r="R30" t="n">
-        <v>7040083</v>
+        <v>7040162</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111947443</v>
+        <v>111947470</v>
       </c>
       <c r="B31" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533920</v>
+        <v>533763</v>
       </c>
       <c r="R31" t="n">
-        <v>7040048</v>
+        <v>7040240</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,37 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111947457</v>
+        <v>111947448</v>
       </c>
       <c r="B32" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533704</v>
+        <v>533870</v>
       </c>
       <c r="R32" t="n">
-        <v>7040176</v>
+        <v>7040086</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111947453</v>
+        <v>111947424</v>
       </c>
       <c r="B33" t="n">
-        <v>89706</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533776</v>
+        <v>534026</v>
       </c>
       <c r="R33" t="n">
-        <v>7040098</v>
+        <v>7039920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,12 +3747,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3939,37 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111947454</v>
+        <v>111947456</v>
       </c>
       <c r="B34" t="n">
-        <v>78740</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533763</v>
+        <v>533757</v>
       </c>
       <c r="R34" t="n">
-        <v>7040093</v>
+        <v>7040083</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,6 +3873,1073 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>111947478</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>533832</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7040203</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>111947454</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>533763</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7040094</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111947475</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>533808</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7040253</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111947442</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>533853</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7040037</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111947443</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>533920</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7040047</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111947445</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>533894</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7040097</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111947447</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>533878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7040114</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>111947471</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>533764</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7040257</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>111947436</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>533726</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7040056</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111947459</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>533705</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7040162</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111947438</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>533737</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7040063</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51287-2025 artfynd.xlsx
+++ b/artfynd/A 51287-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947452</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947467</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947451</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947453</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947464</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947433</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947476</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947434</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947465</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947446</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947479</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947432</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947463</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947440</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947457</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947473</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947480</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947437</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947460</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947477</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947439</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947461</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947470</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947448</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947424</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947456</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947478</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947454</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947475</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947442</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947443</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947445</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947447</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947471</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947436</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947459</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,8 +5160,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>